--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484700_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484700_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2725</v>
+        <v>5.3441</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0374</v>
+        <v>2.2576</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2351</v>
+        <v>3.0864</v>
       </c>
       <c r="G2" t="n">
         <v>4.6189</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0751</v>
+        <v>1.1467</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5837</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4914</v>
+        <v>0.3427</v>
       </c>
       <c r="V2" t="n">
         <v>0.3115</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7583</v>
+        <v>4.104</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2797</v>
+        <v>2.0218</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4786</v>
+        <v>2.0822</v>
       </c>
       <c r="G3" t="n">
         <v>1.8287</v>
@@ -688,13 +688,13 @@
         <v>0.9163</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0683</v>
+        <v>0.414</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5143</v>
+        <v>0.2278</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5826</v>
+        <v>0.1862</v>
       </c>
       <c r="V3" t="n">
         <v>0.945</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8391</v>
+        <v>2.6771</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2539</v>
+        <v>1.1166</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5853</v>
+        <v>1.5605</v>
       </c>
       <c r="G4" t="n">
         <v>1.1798</v>
@@ -766,13 +766,13 @@
         <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5914</v>
       </c>
       <c r="T4" t="n">
-        <v>0.457</v>
+        <v>0.3198</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2964</v>
+        <v>0.2717</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0104</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0568</v>
+        <v>1.8195</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0318</v>
+        <v>0.9304</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0886</v>
+        <v>0.8891</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7293</v>
+        <v>1.7413</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9089</v>
+        <v>0.8181</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8205</v>
+        <v>0.9232</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5723</v>
+        <v>1.7505</v>
       </c>
       <c r="K5" t="n">
-        <v>1.489</v>
+        <v>1.0837</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0833</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.157</v>
+        <v>-0.0092</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2656</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7371</v>
+        <v>0.2564</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>1.105</v>
+        <v>0.0049</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8228</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2823</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.905</v>
+        <v>1.6529</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0093</v>
+        <v>-0.3614</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8957000000000001</v>
+        <v>2.0143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4086</v>
+        <v>1.7293</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0272</v>
+        <v>0.9089</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4358</v>
+        <v>0.8205</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3494</v>
+        <v>1.5723</v>
       </c>
       <c r="K6" t="n">
-        <v>0.907</v>
+        <v>1.489</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5577</v>
+        <v>0.0833</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0593</v>
+        <v>0.157</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9342</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9935</v>
+        <v>0.7371</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2844</v>
+        <v>0.7012</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2255</v>
+        <v>0.4932</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0589</v>
+        <v>0.2079</v>
       </c>
       <c r="V6" t="n">
-        <v>0.945</v>
+        <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5692</v>
+        <v>1.125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7792</v>
+        <v>0.254</v>
       </c>
       <c r="F8" t="n">
-        <v>0.79</v>
+        <v>0.871</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7413</v>
+        <v>0.4086</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8181</v>
+        <v>-0.0272</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9232</v>
+        <v>0.4358</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7505</v>
+        <v>0.3494</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0837</v>
+        <v>0.907</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6667999999999999</v>
+        <v>-0.5577</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0092</v>
+        <v>0.0593</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2656</v>
+        <v>-0.9342</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2564</v>
+        <v>0.9935</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2454</v>
+        <v>0.5043</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0551</v>
+        <v>0.4702</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1903</v>
+        <v>0.0341</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6231</v>
+        <v>0.945</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>E. NAVARRO VALDÉS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7585</v>
+        <v>0.6502</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3596</v>
+        <v>0.6502</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1181</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2571</v>
+        <v>0.6502</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6032</v>
+        <v>0.6502</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3461</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7269</v>
+        <v>0.6502</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1116</v>
+        <v>0.6502</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6153</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4698</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4916</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9614</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9973</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9329</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0644</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9346</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDÉS</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6502</v>
+        <v>0.5787</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6502</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6502</v>
+        <v>2.7245</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6502</v>
+        <v>0.0669</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.6576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6502</v>
+        <v>1.9678</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6502</v>
+        <v>0.6562</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.3116</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.7567</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.346</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.7705</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.7726</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.0021</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6277</v>
+        <v>0.1787</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1148</v>
+        <v>-0.8404</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5129</v>
+        <v>1.019</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7245</v>
+        <v>-0.2571</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0669</v>
+        <v>-0.6032</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6576</v>
+        <v>0.3461</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9678</v>
+        <v>-0.7269</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6562</v>
+        <v>-0.1116</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3116</v>
+        <v>-0.6153</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7567</v>
+        <v>0.4698</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5893</v>
+        <v>-0.4916</v>
       </c>
       <c r="O11" t="n">
-        <v>1.346</v>
+        <v>0.9614</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8195</v>
+        <v>0.4174</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8959</v>
+        <v>0.4521</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0764</v>
+        <v>-0.0347</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.267</v>
+        <v>0.9346</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4195</v>
+        <v>-0.841</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9338</v>
+        <v>-0.9994</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4857</v>
+        <v>0.1584</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4554</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5872</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7896</v>
+        <v>0.1448</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7976</v>
+        <v>-0.1535</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0104</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9334</v>
+        <v>-2.4661</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8945</v>
+        <v>-2.5509</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.039</v>
+        <v>0.0849</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2565</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6323</v>
+        <v>-0.165</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3303</v>
+        <v>0.0132</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.302</v>
+        <v>-0.1782</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.3532</v>
+        <v>-3.9908</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.6056</v>
+        <v>-5.0698</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2524</v>
+        <v>1.079</v>
       </c>
       <c r="G14" t="n">
         <v>0.0408</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1503</v>
+        <v>0.2121</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4042</v>
+        <v>0.1316</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2539</v>
+        <v>0.0805</v>
       </c>
       <c r="V14" t="n">
         <v>-0.945</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.3317</v>
+        <v>12.4328</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.100299999999999</v>
+        <v>-0.999299999999999</v>
       </c>
       <c r="F15" t="n">
         <v>13.432</v>
@@ -1606,7 +1606,7 @@
         <v>-3.2038</v>
       </c>
       <c r="M15" t="n">
-        <v>4.126</v>
+        <v>4.125999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-6.9305</v>
@@ -1624,13 +1624,13 @@
         <v>12.8279</v>
       </c>
       <c r="S15" t="n">
-        <v>3.487899999999999</v>
+        <v>4.5888</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8243</v>
+        <v>3.9254</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6636000000000002</v>
+        <v>0.6633000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.5368</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1269</v>
+        <v>1.3863</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4297</v>
+        <v>0.3335</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6973</v>
+        <v>1.0528</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6816</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0998</v>
+        <v>0.1595</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1441</v>
+        <v>0.0479</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2439</v>
+        <v>0.1116</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2907</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.1545</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7583</v>
+        <v>0.9506</v>
       </c>
       <c r="F17" t="n">
         <v>0.2039</v>
@@ -1780,10 +1780,10 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3115</v>
+        <v>-0.1192</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U17" t="n">
         <v>0.0188</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3678</v>
+        <v>0.3251</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8663</v>
+        <v>0.3251</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4985</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4767</v>
+        <v>0.3251</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1851</v>
+        <v>0.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2916</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9395</v>
+        <v>0.3251</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8978</v>
+        <v>0.3251</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4627</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7127</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2499</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4695</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2542</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2154</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.212</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3251</v>
+        <v>-0.0607</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3251</v>
+        <v>0.5778</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.6385</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3251</v>
+        <v>2.4767</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3251</v>
+        <v>1.1851</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.2916</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3251</v>
+        <v>2.9395</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3251</v>
+        <v>2.8978</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.4627</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.7127</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.2499</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0343</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.212</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2463</v>
+        <v>-0.4152</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0472</v>
+        <v>-0.8164</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2934</v>
+        <v>0.4012</v>
       </c>
       <c r="G20" t="n">
         <v>-2.036</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>1.146</v>
+        <v>0.4846</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0973</v>
+        <v>0.3281</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0487</v>
+        <v>0.1565</v>
       </c>
       <c r="V20" t="n">
         <v>-0.513</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5172</v>
+        <v>-0.5216</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9126</v>
+        <v>-1.2972</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3954</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4252</v>
@@ -2092,13 +2092,13 @@
         <v>2.3823</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1723</v>
+        <v>0.168</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6018</v>
+        <v>0.2172</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4295</v>
+        <v>-0.0492</v>
       </c>
       <c r="V21" t="n">
         <v>0.4528</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1272</v>
+        <v>-0.5809</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1784</v>
+        <v>-1.7938</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0512</v>
+        <v>1.2128</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3191</v>
@@ -2170,13 +2170,13 @@
         <v>2.7489</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7716</v>
+        <v>-0.2253</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.552</v>
+        <v>-0.1674</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2196</v>
+        <v>-0.0579</v>
       </c>
       <c r="V22" t="n">
         <v>0.1309</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8151</v>
+        <v>-0.6772</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2035</v>
+        <v>0.2773</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6116</v>
+        <v>-0.9545</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4748</v>
@@ -2248,13 +2248,13 @@
         <v>2.3823</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5785</v>
+        <v>-0.4406</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7353</v>
+        <v>-0.2545</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.1861</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3115</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9937</v>
+        <v>-1.9019</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0098</v>
+        <v>-2.2982</v>
       </c>
       <c r="F24" t="n">
-        <v>0.016</v>
+        <v>0.3963</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2894</v>
@@ -2326,13 +2326,13 @@
         <v>2.7489</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1022</v>
+        <v>-0.0104</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5098</v>
+        <v>0.2214</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.612</v>
+        <v>-0.2317</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5026</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9028</v>
+        <v>-2.7707</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3223</v>
+        <v>-4.6492</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4195</v>
+        <v>1.8784</v>
       </c>
       <c r="G25" t="n">
         <v>-3.5307</v>
@@ -2404,13 +2404,13 @@
         <v>2.5656</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7099</v>
+        <v>-0.5779</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2111</v>
+        <v>-0.5381</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4987</v>
+        <v>-0.0398</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3115</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.004</v>
+        <v>-4.7053</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.1378</v>
+        <v>-5.0416</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1338</v>
+        <v>0.3363</v>
       </c>
       <c r="G26" t="n">
         <v>-4.6891</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7023</v>
+        <v>-0.4037</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4419</v>
+        <v>-0.3458</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2604</v>
+        <v>-0.0579</v>
       </c>
       <c r="V26" t="n">
         <v>0.7539</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.3317</v>
+        <v>-8.767600000000002</v>
       </c>
       <c r="E27" t="n">
-        <v>-13.4322</v>
+        <v>-13.4321</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1004</v>
+        <v>4.6644</v>
       </c>
       <c r="G27" t="n">
         <v>-14.5537</v>
@@ -2560,13 +2560,13 @@
         <v>21.0745</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.488</v>
+        <v>-0.9238999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6634</v>
+        <v>-0.6635</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.8244</v>
+        <v>-0.2603</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5367</v>
